--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,51 +787,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137041615</v>
+        <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>96792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Korsbacken, Ög</t>
+          <t>Hålaveden, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487792</v>
+        <v>487551</v>
       </c>
       <c r="R3" t="n">
-        <v>6445254</v>
+        <v>6445267</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,77 +859,81 @@
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041615</t>
+          <t>https://artportalen.se/Sighting/137048557</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137041634</v>
+        <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>93451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487765</v>
+        <v>487792</v>
       </c>
       <c r="R4" t="n">
-        <v>6445257</v>
+        <v>6445254</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,6 +985,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,13 +1003,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041634</t>
+          <t>https://artportalen.se/Sighting/137041615</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137041646</v>
+        <v>137041634</v>
       </c>
       <c r="B5" t="n">
         <v>58005</v>
@@ -1036,7 +1042,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1046,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487772</v>
+        <v>487765</v>
       </c>
       <c r="R5" t="n">
-        <v>6445235</v>
+        <v>6445257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,13 +1113,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041646</t>
+          <t>https://artportalen.se/Sighting/137041634</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137041697</v>
+        <v>137041646</v>
       </c>
       <c r="B6" t="n">
         <v>58005</v>
@@ -1146,7 +1152,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1156,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487492</v>
+        <v>487772</v>
       </c>
       <c r="R6" t="n">
-        <v>6445292</v>
+        <v>6445235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,13 +1223,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041697</t>
+          <t>https://artportalen.se/Sighting/137041646</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137041711</v>
+        <v>137041697</v>
       </c>
       <c r="B7" t="n">
         <v>58005</v>
@@ -1266,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487460</v>
+        <v>487492</v>
       </c>
       <c r="R7" t="n">
-        <v>6445222</v>
+        <v>6445292</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,48 +1333,48 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041711</t>
+          <t>https://artportalen.se/Sighting/137041697</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137030558</v>
+        <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487673</v>
+        <v>487460</v>
       </c>
       <c r="R8" t="n">
-        <v>6445314</v>
+        <v>6445222</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,19 +1415,9 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,24 +1432,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Grimlycke</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137030558</t>
+          <t>https://artportalen.se/Sighting/137041711</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137041672</v>
+        <v>137030558</v>
       </c>
       <c r="B9" t="n">
         <v>58169</v>
@@ -1481,14 +1477,14 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1496,13 +1492,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487768</v>
+        <v>487673</v>
       </c>
       <c r="R9" t="n">
-        <v>6445234</v>
+        <v>6445314</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,9 +1525,19 @@
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,59 +1552,59 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Anna Grimlycke</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041672</t>
+          <t>https://artportalen.se/Sighting/137030558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137041787</v>
+        <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>99359</v>
+        <v>58169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1606,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>487679</v>
+        <v>487768</v>
       </c>
       <c r="R10" t="n">
-        <v>6445122</v>
+        <v>6445234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1656,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1668,41 +1673,45 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041787</t>
+          <t>https://artportalen.se/Sighting/137041672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137041723</v>
+        <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>106500</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1713,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487450</v>
+        <v>487679</v>
       </c>
       <c r="R11" t="n">
-        <v>6445271</v>
+        <v>6445122</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,16 +1784,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041723</t>
+          <t>https://artportalen.se/Sighting/137041787</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137041745</v>
+        <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487423</v>
+        <v>487450</v>
       </c>
       <c r="R12" t="n">
-        <v>6445234</v>
+        <v>6445271</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,16 +1891,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041745</t>
+          <t>https://artportalen.se/Sighting/137041723</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137041602</v>
+        <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>101569</v>
+        <v>106502</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1899,21 +1908,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487795</v>
+        <v>487423</v>
       </c>
       <c r="R13" t="n">
-        <v>6445253</v>
+        <v>6445234</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,16 +1998,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137041602</t>
+          <t>https://artportalen.se/Sighting/137041745</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137041686</v>
+        <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>101569</v>
+        <v>106502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,41 +2015,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Korsbacken, Ög</t>
+          <t>Hålaveden, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487514</v>
+        <v>487444</v>
       </c>
       <c r="R14" t="n">
-        <v>6445262</v>
+        <v>6445289</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,34 +2081,257 @@
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Elinne Lotz</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137048558</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137041602</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Korsbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>487795</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6445253</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Trehörna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137041602</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137041686</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korsbacken, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>487514</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6445262</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ödeshög</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Trehörna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137041686</t>
         </is>
@@ -2115,6 +2352,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137041634</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137041646</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137041697</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137030558</v>
       </c>
       <c r="B9" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137041634</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>137041646</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>137041697</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>137030558</v>
       </c>
       <c r="B9" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -1040,11 +1040,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1150,11 +1146,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1260,11 +1252,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1370,11 +1358,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1600,11 +1584,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137041634</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137041646</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>137041697</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>137030558</v>
       </c>
       <c r="B9" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137041634</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137041646</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>137041697</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>137030558</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137041634</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137041646</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>137041697</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>137030558</v>
       </c>
       <c r="B9" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36824-2026 artfynd.xlsx
+++ b/artfynd/A 36824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137041839</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137048557</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>137041615</v>
       </c>
       <c r="B4" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>137041634</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>137041646</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>137041697</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>137041711</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>137030558</v>
       </c>
       <c r="B9" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>137041672</v>
       </c>
       <c r="B10" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>137041787</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>137041723</v>
       </c>
       <c r="B12" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>137041745</v>
       </c>
       <c r="B13" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>137048558</v>
       </c>
       <c r="B14" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>137041602</v>
       </c>
       <c r="B15" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137041686</v>
       </c>
       <c r="B16" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
